--- a/revision/Revision_taxonomica_arboretum.xlsx
+++ b/revision/Revision_taxonomica_arboretum.xlsx
@@ -776,9 +776,21 @@
           <t>Fila sin datos — revisar/eliminar</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -819,9 +831,21 @@
           <t>Quitar el '?'; duplica a Cinnamomum camphora</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>(L.) J.Presl</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -862,9 +886,21 @@
           <t>Autor correcto (André) Rehder; el 'L.' es erróneo</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>(André) Rehder</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -905,9 +941,21 @@
           <t>Autor ya presente</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>(Gordon &amp; Glend.) Lindl. ex Hildebr.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -944,9 +992,21 @@
         <v>2</v>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -987,9 +1047,21 @@
           <t>Nombre común ('Ginkgo') no coincide</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Thunb.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1026,9 +1098,21 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
-      <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1069,9 +1153,21 @@
           <t>Araucariaceae (conífera s.l.)</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>(Lamb.) Rich. &amp; A.Rich.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1108,9 +1204,21 @@
         <v>2</v>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Hook.</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1147,9 +1255,21 @@
         <v>1</v>
       </c>
       <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>(D.Don) Pic.Serm. &amp; Bizzarri</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1190,9 +1310,21 @@
           <t>Corregir a 'Brahea armata'; nombre común ('Damasco') no coincide</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>S.Watson</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Palmera</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1229,9 +1361,21 @@
           <t>Verificar nombre (Callistemon hoy en Melaleuca) y autor</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1268,9 +1412,21 @@
         <v>1</v>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>(Torr.) Florin</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1311,9 +1467,21 @@
           <t>No es conífera aunque lo parezca</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1354,9 +1522,21 @@
           <t>Nombre común ('Abeto de Douglas') no coincide</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr"/>
-      <c r="J17" s="8" t="inlineStr"/>
-      <c r="K17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Eschsch.</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1393,9 +1573,21 @@
         <v>3</v>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr"/>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>(Endl.) Manetti ex Carrière</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1432,9 +1624,21 @@
         <v>1</v>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>(Roxb. ex D. Don) G. Don</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1467,9 +1671,21 @@
           <t>Sin especie determinada</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1502,9 +1718,21 @@
           <t>Typo (backtick); unificar con 'Cedrus sp.'</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1545,9 +1773,21 @@
           <t>Nombre común ('Carex') no coincide</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr"/>
-      <c r="J22" s="8" t="inlineStr"/>
-      <c r="K22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Gillies ex Planch.</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1584,9 +1824,21 @@
         <v>2</v>
       </c>
       <c r="H23" s="6" t="inlineStr"/>
-      <c r="I23" s="8" t="inlineStr"/>
-      <c r="J23" s="8" t="inlineStr"/>
-      <c r="K23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>(A.Murray bis) Parl.</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1623,9 +1875,21 @@
         <v>1</v>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr"/>
-      <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>(Siebold &amp; Zucc.) Endl.</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -1662,9 +1926,21 @@
         <v>1</v>
       </c>
       <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr"/>
-      <c r="J25" s="8" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>(L.) J.Presl</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1701,9 +1977,21 @@
           <t>Árbol pequeño/arbusto; sin especie determinada</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr"/>
-      <c r="J26" s="8" t="inlineStr"/>
-      <c r="K26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1740,9 +2028,21 @@
         <v>1</v>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="8" t="inlineStr"/>
-      <c r="J27" s="8" t="inlineStr"/>
-      <c r="K27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>(Thunb. ex L. f.) D. Don</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1783,9 +2083,21 @@
           <t>Typo con tilde; unificar con Cryptomeria japonica</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr"/>
-      <c r="J28" s="8" t="inlineStr"/>
-      <c r="K28" s="8" t="inlineStr"/>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>(Thunb. ex L. f.) D. Don</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1826,9 +2138,21 @@
           <t>'topacio' parece cultivar; revisar</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr"/>
-      <c r="J29" s="8" t="inlineStr"/>
-      <c r="K29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Hartw. ex Gordon</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1861,9 +2185,21 @@
         <v>2</v>
       </c>
       <c r="H30" s="6" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr"/>
-      <c r="J30" s="8" t="inlineStr"/>
-      <c r="K30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -1900,9 +2236,21 @@
         <v>3</v>
       </c>
       <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="8" t="inlineStr"/>
-      <c r="J31" s="8" t="inlineStr"/>
-      <c r="K31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>Jacq.</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -1939,9 +2287,21 @@
         <v>1</v>
       </c>
       <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr"/>
-      <c r="J32" s="8" t="inlineStr"/>
-      <c r="K32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>F.Muell. ex Benth.</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -1978,9 +2338,21 @@
         <v>2</v>
       </c>
       <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr"/>
-      <c r="J33" s="8" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Labill.</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2013,9 +2385,21 @@
           <t>Nombre común ('Espino') no coincide</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr"/>
-      <c r="J34" s="8" t="inlineStr"/>
-      <c r="K34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2052,9 +2436,21 @@
         <v>1</v>
       </c>
       <c r="H35" s="6" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr"/>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2095,9 +2491,21 @@
           <t>Nombre común ('Boj común') no coincide</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr"/>
-      <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Vahl</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -2138,9 +2546,21 @@
           <t>Typo: 'excelsior'; nombre común ('Duraznero') no coincide</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr"/>
-      <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2181,9 +2601,21 @@
           <t>No es conífera ni latifoliada; hoja caduca en abanico</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr"/>
-      <c r="J38" s="8" t="inlineStr"/>
-      <c r="K38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -2224,9 +2656,21 @@
           <t>Híbrido</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr"/>
-      <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>André</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -2263,9 +2707,21 @@
           <t>También cultivado como arbusto; nombre común ('Falso muérdago') no coincide</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr"/>
-      <c r="J40" s="8" t="inlineStr"/>
-      <c r="K40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -2306,9 +2762,21 @@
           <t>Conífera caduca</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr"/>
-      <c r="J41" s="8" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -2349,9 +2817,21 @@
           <t>Familia en base ('Olives') → Oleaceae</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr"/>
-      <c r="J42" s="8" t="inlineStr"/>
-      <c r="K42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>W.T.Aiton</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -2388,9 +2868,21 @@
         <v>1</v>
       </c>
       <c r="H43" s="6" t="inlineStr"/>
-      <c r="I43" s="8" t="inlineStr"/>
-      <c r="J43" s="8" t="inlineStr"/>
-      <c r="K43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>Hance</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -2423,9 +2915,21 @@
         <v>1</v>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
-      <c r="I44" s="8" t="inlineStr"/>
-      <c r="J44" s="8" t="inlineStr"/>
-      <c r="K44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -2462,9 +2966,21 @@
         <v>1</v>
       </c>
       <c r="H45" s="6" t="inlineStr"/>
-      <c r="I45" s="8" t="inlineStr"/>
-      <c r="J45" s="8" t="inlineStr"/>
-      <c r="K45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -2501,9 +3017,21 @@
         <v>1</v>
       </c>
       <c r="H46" s="6" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr"/>
-      <c r="J46" s="8" t="inlineStr"/>
-      <c r="K46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -2540,9 +3068,21 @@
         <v>1</v>
       </c>
       <c r="H47" s="6" t="inlineStr"/>
-      <c r="I47" s="8" t="inlineStr"/>
-      <c r="J47" s="8" t="inlineStr"/>
-      <c r="K47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -2579,9 +3119,21 @@
         <v>1</v>
       </c>
       <c r="H48" s="6" t="inlineStr"/>
-      <c r="I48" s="8" t="inlineStr"/>
-      <c r="J48" s="8" t="inlineStr"/>
-      <c r="K48" s="8" t="inlineStr"/>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>(Mirb.) Oerst.</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -2622,9 +3174,21 @@
           <t>Quitar el '2'</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr"/>
-      <c r="J49" s="8" t="inlineStr"/>
-      <c r="K49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>(Mirb.) Oerst.</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -2653,9 +3217,21 @@
         <v>1</v>
       </c>
       <c r="H50" s="6" t="inlineStr"/>
-      <c r="I50" s="8" t="inlineStr"/>
-      <c r="J50" s="8" t="inlineStr"/>
-      <c r="K50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -2692,9 +3268,21 @@
         <v>1</v>
       </c>
       <c r="H51" s="6" t="inlineStr"/>
-      <c r="I51" s="8" t="inlineStr"/>
-      <c r="J51" s="8" t="inlineStr"/>
-      <c r="K51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Schltdl. &amp; Cham.</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -2731,9 +3319,21 @@
         <v>2</v>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
-      <c r="I52" s="8" t="inlineStr"/>
-      <c r="J52" s="8" t="inlineStr"/>
-      <c r="K52" s="8" t="inlineStr"/>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>D.Don</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -2766,9 +3366,21 @@
         <v>1</v>
       </c>
       <c r="H53" s="6" t="inlineStr"/>
-      <c r="I53" s="8" t="inlineStr"/>
-      <c r="J53" s="8" t="inlineStr"/>
-      <c r="K53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -2809,9 +3421,21 @@
           <t>Híbrido</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr"/>
-      <c r="J54" s="8" t="inlineStr"/>
-      <c r="K54" s="8" t="inlineStr"/>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Mill. ex Münchh.</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -2852,9 +3476,21 @@
           <t>Typo: 'Populus'</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr"/>
-      <c r="J55" s="8" t="inlineStr"/>
-      <c r="K55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -2891,9 +3527,21 @@
         <v>1</v>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
-      <c r="I56" s="8" t="inlineStr"/>
-      <c r="J56" s="8" t="inlineStr"/>
-      <c r="K56" s="8" t="inlineStr"/>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>M.Roem.</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -2930,9 +3578,21 @@
         <v>1</v>
       </c>
       <c r="H57" s="6" t="inlineStr"/>
-      <c r="I57" s="8" t="inlineStr"/>
-      <c r="J57" s="8" t="inlineStr"/>
-      <c r="K57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>Griff.</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -2969,9 +3629,21 @@
         <v>1</v>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
-      <c r="I58" s="8" t="inlineStr"/>
-      <c r="J58" s="8" t="inlineStr"/>
-      <c r="K58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -3008,9 +3680,21 @@
         <v>3</v>
       </c>
       <c r="H59" s="6" t="inlineStr"/>
-      <c r="I59" s="8" t="inlineStr"/>
-      <c r="J59" s="8" t="inlineStr"/>
-      <c r="K59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -3043,9 +3727,21 @@
           <t>Nombre común ('Olmo') no coincide</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr"/>
-      <c r="J60" s="8" t="inlineStr"/>
-      <c r="K60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -3070,9 +3766,21 @@
           <t>Fila placeholder — completar o eliminar</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr"/>
-      <c r="J61" s="8" t="inlineStr"/>
-      <c r="K61" s="8" t="inlineStr"/>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -3113,9 +3821,21 @@
           <t>Sinónimo; nombre aceptado hoy: Juniperus virginiana L.</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr"/>
-      <c r="J62" s="8" t="inlineStr"/>
-      <c r="K62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>(L.) Antoine</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -3156,9 +3876,21 @@
           <t>Typo: 'sempervirens'</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr"/>
-      <c r="J63" s="8" t="inlineStr"/>
-      <c r="K63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>(D.Don) Endl.</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -3195,9 +3927,21 @@
         <v>1</v>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
-      <c r="I64" s="8" t="inlineStr"/>
-      <c r="J64" s="8" t="inlineStr"/>
-      <c r="K64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>(Lindl.) J.Buchholz</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -3234,9 +3978,21 @@
         <v>3</v>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr"/>
-      <c r="J65" s="8" t="inlineStr"/>
-      <c r="K65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>Lour.</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Arbusto</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -3277,9 +4033,21 @@
           <t>Conífera caduca</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr"/>
-      <c r="J66" s="8" t="inlineStr"/>
-      <c r="K66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>Ten.</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>Conífera</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -3312,9 +4080,21 @@
         <v>1</v>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
-      <c r="I67" s="8" t="inlineStr"/>
-      <c r="J67" s="8" t="inlineStr"/>
-      <c r="K67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>Árbol latifoliado</t>
+        </is>
+      </c>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
